--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo001.xlsx
@@ -4,53 +4,738 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2720" windowWidth="14660" windowHeight="3600"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="货币对的数据字典" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="235">
   <si>
     <t>货币对</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>交易日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>收盘价（元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最高价（元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低价（元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中间价（元）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报价单位</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据来源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>开盘价（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>收盘价（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中间价（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最高价（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最低价（元）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>USD/TWD</t>
+  </si>
+  <si>
+    <t>AUD/CAD</t>
+  </si>
+  <si>
+    <t>AUD/CHF</t>
+  </si>
+  <si>
+    <t>AUD/CNY</t>
+  </si>
+  <si>
+    <t>AUD/DKK</t>
+  </si>
+  <si>
+    <t>AUD/EUR</t>
+  </si>
+  <si>
+    <t>AUD/GBP</t>
+  </si>
+  <si>
+    <t>AUD/HKD</t>
+  </si>
+  <si>
+    <t>AUD/JPY</t>
+  </si>
+  <si>
+    <t>AUD/MOP</t>
+  </si>
+  <si>
+    <t>AUD/RUB</t>
+  </si>
+  <si>
+    <t>AUD/SEK</t>
+  </si>
+  <si>
+    <t>AUD/SGD</t>
+  </si>
+  <si>
+    <t>AUD/TWD</t>
+  </si>
+  <si>
+    <t>AUD/USD</t>
+  </si>
+  <si>
+    <t>CAD/AUD</t>
+  </si>
+  <si>
+    <t>CAD/CHF</t>
+  </si>
+  <si>
+    <t>CAD/CNY</t>
+  </si>
+  <si>
+    <t>CAD/DKK</t>
+  </si>
+  <si>
+    <t>CAD/EUR</t>
+  </si>
+  <si>
+    <t>CAD/GBP</t>
+  </si>
+  <si>
+    <t>CAD/HKD</t>
+  </si>
+  <si>
+    <t>CAD/JPY</t>
+  </si>
+  <si>
+    <t>CAD/MOP</t>
+  </si>
+  <si>
+    <t>CAD/RUB</t>
+  </si>
+  <si>
+    <t>CAD/SEK</t>
+  </si>
+  <si>
+    <t>CAD/SGD</t>
+  </si>
+  <si>
+    <t>CAD/TWD</t>
+  </si>
+  <si>
+    <t>CAD/USD</t>
+  </si>
+  <si>
+    <t>CHF/AUD</t>
+  </si>
+  <si>
+    <t>CHF/CAD</t>
+  </si>
+  <si>
+    <t>CHF/CNY</t>
+  </si>
+  <si>
+    <t>CHF/DKK</t>
+  </si>
+  <si>
+    <t>CHF/EUR</t>
+  </si>
+  <si>
+    <t>CHF/GBP</t>
+  </si>
+  <si>
+    <t>CHF/HKD</t>
+  </si>
+  <si>
+    <t>CHF/JPY</t>
+  </si>
+  <si>
+    <t>CHF/MOP</t>
+  </si>
+  <si>
+    <t>CHF/RUB</t>
+  </si>
+  <si>
+    <t>CHF/SEK</t>
+  </si>
+  <si>
+    <t>CHF/SGD</t>
+  </si>
+  <si>
+    <t>CHF/TWD</t>
+  </si>
+  <si>
+    <t>CHF/USD</t>
+  </si>
+  <si>
+    <t>CNY/AED</t>
+  </si>
+  <si>
+    <t>CNY/AUD</t>
+  </si>
+  <si>
+    <t>CNY/CAD</t>
+  </si>
+  <si>
+    <t>CNY/CHF</t>
+  </si>
+  <si>
+    <t>CNY/DKK</t>
+  </si>
+  <si>
+    <t>CNY/EUR</t>
+  </si>
+  <si>
+    <t>CNY/GBP</t>
+  </si>
+  <si>
+    <t>CNY/HKD</t>
+  </si>
+  <si>
+    <t>CNY/HUF</t>
+  </si>
+  <si>
+    <t>CNY/JPY</t>
+  </si>
+  <si>
+    <t>CNY/KHR</t>
+  </si>
+  <si>
+    <t>CNY/KRW</t>
+  </si>
+  <si>
+    <t>CNY/KZT</t>
+  </si>
+  <si>
+    <t>CNY/MNT</t>
+  </si>
+  <si>
+    <t>CNY/MOP</t>
+  </si>
+  <si>
+    <t>CNY/MXN</t>
+  </si>
+  <si>
+    <t>CNY/MYR</t>
+  </si>
+  <si>
+    <t>CNY/NOK</t>
+  </si>
+  <si>
+    <t>CNY/PLN</t>
+  </si>
+  <si>
+    <t>CNY/RUB</t>
+  </si>
+  <si>
+    <t>CNY/SAR</t>
+  </si>
+  <si>
+    <t>CNY/SEK</t>
+  </si>
+  <si>
+    <t>CNY/SGD</t>
+  </si>
+  <si>
+    <t>CNY/THB</t>
+  </si>
+  <si>
+    <t>CNY/TRY</t>
+  </si>
+  <si>
+    <t>CNY/TWD</t>
+  </si>
+  <si>
+    <t>CNY/USD</t>
+  </si>
+  <si>
+    <t>CNY/ZAR</t>
+  </si>
+  <si>
+    <t>DKK/AUD</t>
+  </si>
+  <si>
+    <t>DKK/CAD</t>
+  </si>
+  <si>
+    <t>DKK/CHF</t>
+  </si>
+  <si>
+    <t>DKK/CNY</t>
+  </si>
+  <si>
+    <t>DKK/EUR</t>
+  </si>
+  <si>
+    <t>DKK/GBP</t>
+  </si>
+  <si>
+    <t>DKK/HKD</t>
+  </si>
+  <si>
+    <t>DKK/JPY</t>
+  </si>
+  <si>
+    <t>DKK/MOP</t>
+  </si>
+  <si>
+    <t>DKK/RUB</t>
+  </si>
+  <si>
+    <t>DKK/SEK</t>
+  </si>
+  <si>
+    <t>DKK/SGD</t>
+  </si>
+  <si>
+    <t>DKK/TWD</t>
+  </si>
+  <si>
+    <t>DKK/USD</t>
+  </si>
+  <si>
+    <t>EUR/AUD</t>
+  </si>
+  <si>
+    <t>EUR/CAD</t>
+  </si>
+  <si>
+    <t>EUR/CHF</t>
+  </si>
+  <si>
+    <t>EUR/CNY</t>
+  </si>
+  <si>
+    <t>EUR/DKK</t>
+  </si>
+  <si>
+    <t>EUR/GBP</t>
+  </si>
+  <si>
+    <t>EUR/HKD</t>
+  </si>
+  <si>
+    <t>EUR/JPY</t>
+  </si>
+  <si>
+    <t>EUR/MOP</t>
+  </si>
+  <si>
+    <t>EUR/RUB</t>
+  </si>
+  <si>
+    <t>EUR/SEK</t>
+  </si>
+  <si>
+    <t>EUR/SGD</t>
+  </si>
+  <si>
+    <t>EUR/TWD</t>
+  </si>
+  <si>
+    <t>EUR/USD</t>
+  </si>
+  <si>
+    <t>GBP/AUD</t>
+  </si>
+  <si>
+    <t>GBP/CAD</t>
+  </si>
+  <si>
+    <t>GBP/CHF</t>
+  </si>
+  <si>
+    <t>GBP/CNY</t>
+  </si>
+  <si>
+    <t>GBP/DKK</t>
+  </si>
+  <si>
+    <t>GBP/EUR</t>
+  </si>
+  <si>
+    <t>GBP/HKD</t>
+  </si>
+  <si>
+    <t>GBP/JPY</t>
+  </si>
+  <si>
+    <t>GBP/MOP</t>
+  </si>
+  <si>
+    <t>GBP/RUB</t>
+  </si>
+  <si>
+    <t>GBP/SEK</t>
+  </si>
+  <si>
+    <t>GBP/SGD</t>
+  </si>
+  <si>
+    <t>GBP/TWD</t>
+  </si>
+  <si>
+    <t>GBP/USD</t>
+  </si>
+  <si>
+    <t>HKD/AUD</t>
+  </si>
+  <si>
+    <t>HKD/CAD</t>
+  </si>
+  <si>
+    <t>HKD/CHF</t>
+  </si>
+  <si>
+    <t>HKD/CNY</t>
+  </si>
+  <si>
+    <t>HKD/DKK</t>
+  </si>
+  <si>
+    <t>HKD/EUR</t>
+  </si>
+  <si>
+    <t>HKD/GBP</t>
+  </si>
+  <si>
+    <t>HKD/JPY</t>
+  </si>
+  <si>
+    <t>HKD/MOP</t>
+  </si>
+  <si>
+    <t>HKD/RUB</t>
+  </si>
+  <si>
+    <t>HKD/SEK</t>
+  </si>
+  <si>
+    <t>HKD/SGD</t>
+  </si>
+  <si>
+    <t>HKD/TWD</t>
+  </si>
+  <si>
+    <t>HKD/USD</t>
+  </si>
+  <si>
+    <t>JPY/AUD</t>
+  </si>
+  <si>
+    <t>JPY/CAD</t>
+  </si>
+  <si>
+    <t>JPY/CHF</t>
+  </si>
+  <si>
+    <t>JPY/CNY</t>
+  </si>
+  <si>
+    <t>JPY/DKK</t>
+  </si>
+  <si>
+    <t>JPY/EUR</t>
+  </si>
+  <si>
+    <t>JPY/GBP</t>
+  </si>
+  <si>
+    <t>JPY/HKD</t>
+  </si>
+  <si>
+    <t>JPY/MOP</t>
+  </si>
+  <si>
+    <t>JPY/RUB</t>
+  </si>
+  <si>
+    <t>JPY/SEK</t>
+  </si>
+  <si>
+    <t>JPY/SGD</t>
+  </si>
+  <si>
+    <t>JPY/TWD</t>
+  </si>
+  <si>
+    <t>JPY/USD</t>
+  </si>
+  <si>
+    <t>MOP/AUD</t>
+  </si>
+  <si>
+    <t>MOP/CAD</t>
+  </si>
+  <si>
+    <t>MOP/CHF</t>
+  </si>
+  <si>
+    <t>MOP/CNY</t>
+  </si>
+  <si>
+    <t>MOP/DKK</t>
+  </si>
+  <si>
+    <t>MOP/EUR</t>
+  </si>
+  <si>
+    <t>MOP/GBP</t>
+  </si>
+  <si>
+    <t>MOP/HKD</t>
+  </si>
+  <si>
+    <t>MOP/JPY</t>
+  </si>
+  <si>
+    <t>MOP/RUB</t>
+  </si>
+  <si>
+    <t>MOP/SEK</t>
+  </si>
+  <si>
+    <t>MOP/SGD</t>
+  </si>
+  <si>
+    <t>MOP/TWD</t>
+  </si>
+  <si>
+    <t>MOP/USD</t>
+  </si>
+  <si>
+    <t>NZD/CNY</t>
+  </si>
+  <si>
+    <t>NZD/USD</t>
+  </si>
+  <si>
+    <t>RUB/AUD</t>
+  </si>
+  <si>
+    <t>RUB/CAD</t>
+  </si>
+  <si>
+    <t>RUB/CHF</t>
+  </si>
+  <si>
+    <t>RUB/CNY</t>
+  </si>
+  <si>
+    <t>RUB/DKK</t>
+  </si>
+  <si>
+    <t>RUB/EUR</t>
+  </si>
+  <si>
+    <t>RUB/GBP</t>
+  </si>
+  <si>
+    <t>RUB/HKD</t>
+  </si>
+  <si>
+    <t>RUB/JPY</t>
+  </si>
+  <si>
+    <t>RUB/MOP</t>
+  </si>
+  <si>
+    <t>RUB/SEK</t>
+  </si>
+  <si>
+    <t>RUB/SGD</t>
+  </si>
+  <si>
+    <t>RUB/TWD</t>
+  </si>
+  <si>
+    <t>RUB/USD</t>
+  </si>
+  <si>
+    <t>SEK/AUD</t>
+  </si>
+  <si>
+    <t>SEK/CAD</t>
+  </si>
+  <si>
+    <t>SEK/CHF</t>
+  </si>
+  <si>
+    <t>SEK/CNY</t>
+  </si>
+  <si>
+    <t>SEK/DKK</t>
+  </si>
+  <si>
+    <t>SEK/EUR</t>
+  </si>
+  <si>
+    <t>SEK/GBP</t>
+  </si>
+  <si>
+    <t>SEK/HKD</t>
+  </si>
+  <si>
+    <t>SEK/JPY</t>
+  </si>
+  <si>
+    <t>SEK/MOP</t>
+  </si>
+  <si>
+    <t>SEK/RUB</t>
+  </si>
+  <si>
+    <t>SEK/SGD</t>
+  </si>
+  <si>
+    <t>SEK/TWD</t>
+  </si>
+  <si>
+    <t>SEK/USD</t>
+  </si>
+  <si>
+    <t>SGD/AUD</t>
+  </si>
+  <si>
+    <t>SGD/CAD</t>
+  </si>
+  <si>
+    <t>SGD/CHF</t>
+  </si>
+  <si>
+    <t>SGD/CNY</t>
+  </si>
+  <si>
+    <t>SGD/DKK</t>
+  </si>
+  <si>
+    <t>SGD/EUR</t>
+  </si>
+  <si>
+    <t>SGD/GBP</t>
+  </si>
+  <si>
+    <t>SGD/HKD</t>
+  </si>
+  <si>
+    <t>SGD/JPY</t>
+  </si>
+  <si>
+    <t>SGD/MOP</t>
+  </si>
+  <si>
+    <t>SGD/RUB</t>
+  </si>
+  <si>
+    <t>SGD/SEK</t>
+  </si>
+  <si>
+    <t>SGD/TWD</t>
+  </si>
+  <si>
+    <t>SGD/USD</t>
+  </si>
+  <si>
+    <t>TWD/AUD</t>
+  </si>
+  <si>
+    <t>TWD/CAD</t>
+  </si>
+  <si>
+    <t>TWD/CHF</t>
+  </si>
+  <si>
+    <t>TWD/CNY</t>
+  </si>
+  <si>
+    <t>TWD/DKK</t>
+  </si>
+  <si>
+    <t>TWD/EUR</t>
+  </si>
+  <si>
+    <t>TWD/GBP</t>
+  </si>
+  <si>
+    <t>TWD/HKD</t>
+  </si>
+  <si>
+    <t>TWD/JPY</t>
+  </si>
+  <si>
+    <t>TWD/MOP</t>
+  </si>
+  <si>
+    <t>TWD/RUB</t>
+  </si>
+  <si>
+    <t>TWD/SEK</t>
+  </si>
+  <si>
+    <t>TWD/SGD</t>
+  </si>
+  <si>
+    <t>TWD/USD</t>
+  </si>
+  <si>
+    <t>USD/AUD</t>
+  </si>
+  <si>
+    <t>USD/CAD</t>
+  </si>
+  <si>
+    <t>USD/CHF</t>
+  </si>
+  <si>
+    <t>USD/CNY</t>
+  </si>
+  <si>
+    <t>USD/DKK</t>
+  </si>
+  <si>
+    <t>USD/EUR</t>
+  </si>
+  <si>
+    <t>USD/GBP</t>
+  </si>
+  <si>
+    <t>USD/HKD</t>
+  </si>
+  <si>
+    <t>USD/JPY</t>
+  </si>
+  <si>
+    <t>USD/MOP</t>
+  </si>
+  <si>
+    <t>USD/RUB</t>
+  </si>
+  <si>
+    <t>USD/SEK</t>
+  </si>
+  <si>
+    <t>USD/SGD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -60,6 +745,21 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -86,8 +786,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -392,40 +1096,73 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
-    <col min="6" max="7" width="12.453125" customWidth="1"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+    <col min="3" max="3" width="20.75" customWidth="1"/>
+    <col min="4" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="B3" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="5">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的日期类型" error="正确的日期类型：yyyy/MM/dd" promptTitle="请输入正确的日期类型" prompt="正确的日期类型：yyyy/MM/dd" sqref="B1:B1048576">
+      <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的数字类型" error="请输入正确的数字类型" promptTitle="请输入正确的数字类型" prompt="请输入正确的数字类型" sqref="C1:C1048576 D1:D1048576 E1:E1048576 F1:F1048576 G1:G1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的正整数类型" error="请输入正确的正整数类型" promptTitle="请输入正确的正整数类型" prompt="请输入正确的正整数类型" sqref="H1:H1048576">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="I1:I1048576">
+      <formula1>"BAK:行内,CFETS:外汇交易中心,SAFE:外管局,"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请选择下拉框中的值" error="请选择下拉框中的值" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="A1:A1048576">
+      <formula1>INDIRECT("货币对的数据字典!a1:a226")</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -433,20 +1170,1145 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:A226"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="16.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A48" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A50" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A51" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A53" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A54" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A55" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A56" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A57" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A58" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A60" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A61" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A62" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A65" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A66" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A67" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A69" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A70" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A71" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A72" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A73" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A74" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A75" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A76" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A77" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A78" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A79" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A85" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A86" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A87" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A88" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A89" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A90" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A92" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A93" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A94" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A95" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A96" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A97" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A98" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A100" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A101" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A102" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A103" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A104" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A105" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A106" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A107" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A108" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A109" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A110" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A111" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A112" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A113" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A114" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A115" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A116" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A118" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A119" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A120" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A121" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A122" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A123" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A124" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A125" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A126" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A127" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A128" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A129" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A130" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A131" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A132" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A133" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A134" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A135" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A136" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A137" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A138" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A139" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A140" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A141" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A142" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A143" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A144" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A145" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A146" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A147" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A148" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A149" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A150" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A151" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A152" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A153" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A154" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A155" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A156" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A157" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A158" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A159" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A160" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A161" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A162" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A163" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A164" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A165" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A166" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A167" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A168" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A170" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A171" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A172" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A173" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A174" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A175" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A176" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A177" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A178" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A179" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A180" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A181" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A182" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A183" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A184" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A185" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A186" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A187" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A188" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A189" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A190" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A191" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A192" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A193" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A194" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A195" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A196" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A197" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A198" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A199" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A200" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A201" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A202" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A203" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A204" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A205" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A206" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A207" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A208" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A209" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A210" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A211" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A212" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A213" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A214" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A215" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A216" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A217" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A218" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A219" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A220" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A221" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A222" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A223" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A224" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A225" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ChbExchangeQuotationInfo001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -735,6 +735,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -786,12 +789,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1096,24 +1102,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="18.125" customWidth="1"/>
-    <col min="3" max="3" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="18.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.7265625" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="17.5" customWidth="1"/>
-    <col min="8" max="8" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" customWidth="1"/>
+    <col min="9" max="9" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1138,30 +1144,29 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
-      <c r="B3" s="2"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="5">
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的日期类型" error="正确的日期类型：yyyy/MM/dd" promptTitle="请输入正确的日期类型" prompt="正确的日期类型：yyyy/MM/dd" sqref="B1:B1048576">
+  <dataValidations count="10">
+    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的日期类型" error="正确的日期类型：yyyy/MM/dd" promptTitle="请输入正确的日期类型" prompt="正确的日期类型：yyyy-MM-dd" sqref="B2:B1048576">
       <formula1>1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的数字类型" error="请输入正确的数字类型" promptTitle="请输入正确的数字类型" prompt="请输入正确的数字类型" sqref="C1:C1048576 D1:D1048576 E1:E1048576 F1:F1048576 G1:G1048576">
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的数字类型" error="请输入正确的数字类型" promptTitle="请输入正确的数字类型" prompt="请输入正确的数字类型" sqref="F2:F1048576 C2:C1048576 D2:D1048576 E2:E1048576 G2:G1048576">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的正整数类型" error="请输入正确的正整数类型" promptTitle="请输入正确的正整数类型" prompt="请输入正确的正整数类型" sqref="H1:H1048576">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的正整数类型" error="请输入正确的正整数类型" promptTitle="请输入正确的正整数类型" prompt="请输入正确的正整数类型" sqref="H2:H1048576">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="I1:I1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="I2:I1048576">
       <formula1>"BAK:行内,CFETS:外汇交易中心,SAFE:外管局,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请选择下拉框中的值" error="请选择下拉框中的值" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="A1:A1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请选择下拉框中的值" error="请选择下拉框中的值" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="A2:A1048576">
       <formula1>INDIRECT("货币对的数据字典!a1:a226")</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请选择下拉框中的值" error="请选择下拉框中的值" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="A1"/>
+    <dataValidation operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的数字类型" error="请输入正确的数字类型" promptTitle="请输入正确的数字类型" prompt="请输入正确的数字类型" sqref="C1 D1 E1 F1 G1"/>
+    <dataValidation operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的正整数类型" error="请输入正确的正整数类型" promptTitle="请输入正确的正整数类型" prompt="请输入正确的正整数类型" sqref="H1"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="请选择下拉框中的值" prompt="请选择下拉框中的值" sqref="I1"/>
+    <dataValidation operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="请输入正确的日期类型" error="正确的日期类型：yyyy/MM/dd" promptTitle="请输入正确的日期类型" prompt="正确的日期类型：yyyy-MM-dd" sqref="B1"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1171,1137 +1176,1137 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A226"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.75" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="217" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="218" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="219" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="220" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="221" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="222" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="223" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="224" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="225" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="226" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>9</v>
       </c>
